--- a/exports/ADANIENSOL_full_report.xlsx
+++ b/exports/ADANIENSOL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.41</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44627.55208333334</v>
+        <v>44628.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2207.05</v>
+        <v>2116</v>
       </c>
       <c r="I2" t="n">
         <v>2142.763185286688</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K2" t="n">
-        <v>23.58</v>
+        <v>18.48</v>
       </c>
       <c r="L2" t="n">
         <v>2.46</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>18.06</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44657.55208333334</v>
+        <v>44658.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2482</v>
+        <v>2599.15</v>
       </c>
       <c r="I3" t="n">
         <v>2483.377681948057</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.3</v>
+        <v>-22.83</v>
       </c>
       <c r="L3" t="n">
-        <v>22.11</v>
+        <v>28.28</v>
       </c>
       <c r="M3" t="n">
         <v>3.87</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.39</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44691.38541666666</v>
+        <v>44691.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>2551.6</v>
+        <v>2501.35</v>
       </c>
       <c r="I4" t="n">
         <v>2530.762160745299</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.83</v>
+        <v>-3.76</v>
       </c>
       <c r="L4" t="n">
         <v>8.279999999999999</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.52</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44733.38541666666</v>
+        <v>44733.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>2114.65</v>
+        <v>2219.9</v>
       </c>
       <c r="I5" t="n">
         <v>2217.421184203777</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41.83333333333334</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>15.46</v>
+        <v>11.25</v>
       </c>
       <c r="L5" t="n">
         <v>5.94</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.04</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>3860</v>
+        <v>3749.05</v>
       </c>
       <c r="I6" t="n">
         <v>3815.751010323354</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>94</v>
+        <v>96.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>73.88</v>
+        <v>68.88</v>
       </c>
       <c r="L6" t="n">
         <v>6.26</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.98</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44865.38541666666</v>
+        <v>44865.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>3294.75</v>
+        <v>3351.95</v>
       </c>
       <c r="I7" t="n">
         <v>3333.802775208212</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>12.12</v>
+        <v>10.59</v>
       </c>
       <c r="L7" t="n">
         <v>2.8</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.32</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44882.38541666666</v>
+        <v>44882.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>3225</v>
+        <v>3111.5</v>
       </c>
       <c r="I8" t="n">
         <v>3126.203304275575</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.79</v>
+        <v>-7.17</v>
       </c>
       <c r="L8" t="n">
-        <v>4.38</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>2.24</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.4</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>2821.55</v>
+        <v>2950</v>
       </c>
       <c r="I9" t="n">
         <v>2924.501534826337</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>9.32</v>
+        <v>5.19</v>
       </c>
       <c r="L9" t="n">
         <v>3.66</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>9.81</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2680</v>
+        <v>2643.65</v>
       </c>
       <c r="I10" t="n">
         <v>2669.817336450396</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.15</v>
+        <v>-10.38</v>
       </c>
       <c r="L10" t="n">
-        <v>9.44</v>
+        <v>10.85</v>
       </c>
       <c r="M10" t="n">
         <v>-0</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.98</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44922.55208333334</v>
+        <v>44923.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2490</v>
+        <v>2546.3</v>
       </c>
       <c r="I11" t="n">
         <v>2543.90086793767</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K11" t="n">
-        <v>5.81</v>
+        <v>3.68</v>
       </c>
       <c r="L11" t="n">
         <v>3.68</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>12.82</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44951.38541666666</v>
+        <v>44951.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>2617.85</v>
+        <v>2539.9</v>
       </c>
       <c r="I12" t="n">
         <v>2601.790110907509</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>2.81</v>
+        <v>-0.25</v>
       </c>
       <c r="L12" t="n">
-        <v>4.23</v>
+        <v>4.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.56</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>708.75</v>
+        <v>744.15</v>
       </c>
       <c r="I13" t="n">
         <v>721.7989552833468</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>72.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="L13" t="n">
         <v>3.63</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.94</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1002.55</v>
+        <v>943.4</v>
       </c>
       <c r="I14" t="n">
         <v>994.9022039618109</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K14" t="n">
-        <v>34.72</v>
+        <v>26.78</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1239,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>5.45</v>
+        <v>5.9</v>
       </c>
       <c r="O14" t="n">
         <v>4.99</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>18.32</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45026.55208333334</v>
+        <v>45027.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1000.85</v>
+        <v>1050.85</v>
       </c>
       <c r="I15" t="n">
         <v>1038.083446733102</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.09</v>
+        <v>-11.39</v>
       </c>
       <c r="L15" t="n">
-        <v>6.92</v>
+        <v>11.39</v>
       </c>
       <c r="M15" t="n">
         <v>3.23</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>11.54</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45051.55208333334</v>
+        <v>45054.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>999</v>
+        <v>949.05</v>
       </c>
       <c r="I16" t="n">
         <v>959.3203772307852</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.93</v>
+        <v>-9.69</v>
       </c>
       <c r="L16" t="n">
-        <v>8.59</v>
+        <v>9.69</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9399999999999999</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.11</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>5</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>8.84</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>789.15</v>
+        <v>826.7</v>
       </c>
       <c r="I17" t="n">
         <v>806.6846755865553</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>16.85</v>
+        <v>12.89</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.34</v>
+        <v>4.74</v>
       </c>
       <c r="N17" t="n">
         <v>5.15</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>11.95</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45075.55208333334</v>
+        <v>45076.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>835.85</v>
+        <v>805.3</v>
       </c>
       <c r="I18" t="n">
         <v>828.4754950094449</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.11</v>
+        <v>-2.59</v>
       </c>
       <c r="L18" t="n">
-        <v>0.55</v>
+        <v>4.13</v>
       </c>
       <c r="M18" t="n">
         <v>3.5</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>13.63</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45105.38541666666</v>
+        <v>45105.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>797.85</v>
+        <v>821.5</v>
       </c>
       <c r="I19" t="n">
         <v>813.5816582473291</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.93</v>
+        <v>-2.01</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45120.38541666666</v>
+        <v>45120.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="I20" t="n">
         <v>745.8525691343812</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9.31</v>
       </c>
       <c r="L20" t="n">
-        <v>9.43</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>0.84</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>5.17</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45124.55208333334</v>
+        <v>45125.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>769.9</v>
+        <v>787.9</v>
       </c>
       <c r="I21" t="n">
         <v>776.5570932889057</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.34</v>
+        <v>-5.76</v>
       </c>
       <c r="L21" t="n">
-        <v>3.89</v>
+        <v>8.32</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.88</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45163.55208333334</v>
+        <v>45166.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>872.1</v>
+        <v>870.5</v>
       </c>
       <c r="I22" t="n">
         <v>870.7259854138315</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>10.69</v>
+        <v>10.48</v>
       </c>
       <c r="L22" t="n">
         <v>2.47</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.55</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45225.55208333334</v>
+        <v>45226.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>743.5</v>
+        <v>754.8</v>
       </c>
       <c r="I23" t="n">
         <v>751.7866995060922</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K23" t="n">
-        <v>14.59</v>
+        <v>13.29</v>
       </c>
       <c r="L23" t="n">
         <v>3.27</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>8.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45247.55208333334</v>
+        <v>45250.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>741</v>
+        <v>727.8</v>
       </c>
       <c r="I24" t="n">
         <v>730.0835154690923</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.83</v>
+        <v>-3.58</v>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>3.84</v>
       </c>
       <c r="M24" t="n">
         <v>0.2</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>5.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45254.55208333334</v>
+        <v>45258.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>733</v>
+        <v>857.1</v>
       </c>
       <c r="I25" t="n">
         <v>753.8933037459477</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.71</v>
+        <v>-17.77</v>
       </c>
       <c r="L25" t="n">
-        <v>2.36</v>
+        <v>19.54</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.05</v>
       </c>
       <c r="N25" t="n">
-        <v>1.24</v>
+        <v>19.36</v>
       </c>
       <c r="O25" t="n">
         <v>-1.34</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>14.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1053.15</v>
+        <v>1000</v>
       </c>
       <c r="I26" t="n">
         <v>1015.388141559569</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>22.87</v>
+        <v>16.67</v>
       </c>
       <c r="L26" t="n">
         <v>12.96</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>17.5</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1058</v>
+        <v>1145.05</v>
       </c>
       <c r="I27" t="n">
         <v>1142.003514394728</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.8</v>
+        <v>-14.5</v>
       </c>
       <c r="L27" t="n">
-        <v>8.300000000000001</v>
+        <v>25</v>
       </c>
       <c r="M27" t="n">
-        <v>2.59</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="O27" t="n">
         <v>-7.21</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>10.83</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1088</v>
+        <v>1056.5</v>
       </c>
       <c r="I28" t="n">
         <v>1076.115234298481</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.98</v>
+        <v>-7.73</v>
       </c>
       <c r="L28" t="n">
-        <v>6.38</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="N28" t="n">
         <v>3.28</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>9.94</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45345.55208333334</v>
+        <v>45348.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1083.9</v>
+        <v>1149.8</v>
       </c>
       <c r="I29" t="n">
         <v>1112.596710361529</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.59</v>
+        <v>-8.83</v>
       </c>
       <c r="L29" t="n">
-        <v>8.85</v>
+        <v>9.32</v>
       </c>
       <c r="M29" t="n">
         <v>1.63</v>
       </c>
       <c r="N29" t="n">
-        <v>6.84</v>
+        <v>8.81</v>
       </c>
       <c r="O29" t="n">
         <v>-2.01</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>9.58</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1122.1</v>
+        <v>1083</v>
       </c>
       <c r="I30" t="n">
         <v>1085.99660762876</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.41</v>
+        <v>-5.81</v>
       </c>
       <c r="L30" t="n">
-        <v>5.98</v>
+        <v>6.07</v>
       </c>
       <c r="M30" t="n">
         <v>0.06</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.31</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45365.38541666666</v>
+        <v>45365.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1033</v>
+        <v>1049.6</v>
       </c>
       <c r="I31" t="n">
         <v>1041.782532643946</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>4.62</v>
+        <v>3.08</v>
       </c>
       <c r="L31" t="n">
         <v>4.97</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.75</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1055.1</v>
+        <v>1020</v>
       </c>
       <c r="I32" t="n">
         <v>1023.991029849134</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>53</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K32" t="n">
-        <v>0.52</v>
+        <v>-2.82</v>
       </c>
       <c r="L32" t="n">
         <v>7.44</v>
@@ -2265,7 +2648,7 @@
         <v>3.08</v>
       </c>
       <c r="N32" t="n">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="O32" t="n">
         <v>10.49</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.36</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1043</v>
+        <v>1070.75</v>
       </c>
       <c r="I33" t="n">
         <v>1048.691019341351</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.25</v>
+        <v>-4.98</v>
       </c>
       <c r="L33" t="n">
-        <v>3.75</v>
+        <v>7.31</v>
       </c>
       <c r="M33" t="n">
         <v>0.75</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>7.44</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1227</v>
+        <v>1007.95</v>
       </c>
       <c r="I34" t="n">
         <v>1122.099612363218</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K34" t="n">
-        <v>14.59</v>
+        <v>-5.87</v>
       </c>
       <c r="L34" t="n">
-        <v>3.49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>0.11</v>
+        <v>0.59</v>
       </c>
       <c r="N34" t="n">
-        <v>1.7</v>
+        <v>20.33</v>
       </c>
       <c r="O34" t="n">
         <v>1.94</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>25.55</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45498.38541666666</v>
+        <v>45498.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1035.6</v>
+        <v>1059</v>
       </c>
       <c r="I35" t="n">
         <v>1043.870251320303</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.74</v>
+        <v>-5.06</v>
       </c>
       <c r="L35" t="n">
         <v>21.01</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.42</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45509.55208333334</v>
+        <v>45510.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1164.6</v>
+        <v>1128.9</v>
       </c>
       <c r="I36" t="n">
         <v>1129.892038507057</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>9.970000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="L36" t="n">
         <v>2.55</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>16.78</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45558.55208333334</v>
+        <v>45559.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1022.2</v>
+        <v>1047.35</v>
       </c>
       <c r="I37" t="n">
         <v>1032.736894908458</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K37" t="n">
-        <v>9.449999999999999</v>
+        <v>7.22</v>
       </c>
       <c r="L37" t="n">
         <v>4.83</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.5</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1021.7</v>
+        <v>977.25</v>
       </c>
       <c r="I38" t="n">
         <v>987.4612027079542</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.45</v>
+        <v>-6.69</v>
       </c>
       <c r="L38" t="n">
-        <v>5.09</v>
+        <v>7.19</v>
       </c>
       <c r="M38" t="n">
         <v>1.69</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>5.66</v>
       </c>
       <c r="O38" t="n">
         <v>2.71</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.25</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45572.55208333334</v>
+        <v>45573.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>935</v>
+        <v>1006.9</v>
       </c>
       <c r="I39" t="n">
         <v>1004.592378653261</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>4.32</v>
+        <v>-3.03</v>
       </c>
       <c r="L39" t="n">
         <v>4.43</v>
@@ -2664,7 +3131,7 @@
         <v>1.26</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="O39" t="n">
         <v>-5.66</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>14.04</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45589.55208333334</v>
+        <v>45590.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>975</v>
+        <v>932.5</v>
       </c>
       <c r="I40" t="n">
         <v>971.8049434155588</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.17</v>
+        <v>-7.39</v>
       </c>
       <c r="L40" t="n">
         <v>9.130000000000001</v>
@@ -2721,7 +3200,7 @@
         <v>0.53</v>
       </c>
       <c r="N40" t="n">
-        <v>2.41</v>
+        <v>5.64</v>
       </c>
       <c r="O40" t="n">
         <v>7.83</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>11.11</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45601.38541666666</v>
+        <v>45601.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>968.6</v>
+        <v>1012</v>
       </c>
       <c r="I41" t="n">
         <v>1004.643828114207</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.87</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>6.17</v>
+        <v>9.91</v>
       </c>
       <c r="M41" t="n">
         <v>1.32</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45603.38541666666</v>
+        <v>45603.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>989.05</v>
+        <v>962</v>
       </c>
       <c r="I42" t="n">
         <v>973.0731922645366</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.27</v>
+        <v>-4.94</v>
       </c>
       <c r="L42" t="n">
-        <v>4.46</v>
+        <v>5.5</v>
       </c>
       <c r="M42" t="n">
         <v>6.23</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.16</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45623.55208333334</v>
+        <v>45624.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>660.8</v>
+        <v>726.85</v>
       </c>
       <c r="I43" t="n">
         <v>712.5712163081973</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>31.31</v>
+        <v>24.44</v>
       </c>
       <c r="L43" t="n">
         <v>2.81</v>
@@ -2892,7 +3407,7 @@
         <v>4.49</v>
       </c>
       <c r="N43" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="O43" t="n">
         <v>-10.34</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>19.14</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>780</v>
+        <v>763.1</v>
       </c>
       <c r="I44" t="n">
         <v>771.8353840524242</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K44" t="n">
-        <v>7.31</v>
+        <v>4.99</v>
       </c>
       <c r="L44" t="n">
         <v>5.76</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.91</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>693.05</v>
+        <v>776.85</v>
       </c>
       <c r="I45" t="n">
         <v>755.0023355334125</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>9.18</v>
+        <v>-1.8</v>
       </c>
       <c r="L45" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="M45" t="n">
-        <v>0.73</v>
+        <v>1.43</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>11.54</v>
       </c>
       <c r="O45" t="n">
         <v>-1.28</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>15</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45685.38541666666</v>
+        <v>45685.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>765.5</v>
+        <v>749.8</v>
       </c>
       <c r="I46" t="n">
         <v>750.0646519790204</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.46</v>
+        <v>-3.48</v>
       </c>
       <c r="L46" t="n">
         <v>9.880000000000001</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>648.8</v>
+        <v>701.9</v>
       </c>
       <c r="I47" t="n">
         <v>697.6451381670389</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K47" t="n">
-        <v>13.47</v>
+        <v>6.39</v>
       </c>
       <c r="L47" t="n">
         <v>5.12</v>
@@ -3120,7 +3683,7 @@
         <v>1.28</v>
       </c>
       <c r="N47" t="n">
-        <v>4.17</v>
+        <v>9.06</v>
       </c>
       <c r="O47" t="n">
         <v>-0.5600000000000001</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>12.58</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>858.2</v>
+        <v>802.55</v>
       </c>
       <c r="I48" t="n">
         <v>815.2975465861263</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K48" t="n">
-        <v>22.27</v>
+        <v>14.34</v>
       </c>
       <c r="L48" t="n">
         <v>7.96</v>
       </c>
       <c r="M48" t="n">
-        <v>1.73</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>3.02</v>
+        <v>4.33</v>
       </c>
       <c r="O48" t="n">
         <v>9.06</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>10.68</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>885.2</v>
+        <v>894.35</v>
       </c>
       <c r="I49" t="n">
         <v>888.261113538714</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>-10.3</v>
+        <v>-11.44</v>
       </c>
       <c r="L49" t="n">
-        <v>10.85</v>
+        <v>12.52</v>
       </c>
       <c r="M49" t="n">
         <v>3.08</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>8.5</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45783.55208333334</v>
+        <v>45784.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>904</v>
+        <v>876.35</v>
       </c>
       <c r="I50" t="n">
         <v>882.1303096327964</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>1.08</v>
+        <v>-2.01</v>
       </c>
       <c r="L50" t="n">
-        <v>1.49</v>
+        <v>2.11</v>
       </c>
       <c r="M50" t="n">
-        <v>0.05</v>
+        <v>2.88</v>
       </c>
       <c r="N50" t="n">
         <v>5.77</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>10.96</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>894.95</v>
+        <v>900.9</v>
       </c>
       <c r="I51" t="n">
         <v>897.5888282816212</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.12</v>
+        <v>-2.8</v>
       </c>
       <c r="L51" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="M51" t="n">
         <v>3.46</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>870.55</v>
+        <v>857.1</v>
       </c>
       <c r="I52" t="n">
         <v>867.4202348966603</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.37</v>
+        <v>-4.86</v>
       </c>
       <c r="L52" t="n">
         <v>5.48</v>
       </c>
       <c r="M52" t="n">
-        <v>0.61</v>
+        <v>1.21</v>
       </c>
       <c r="N52" t="n">
         <v>4.23</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.77</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>863</v>
+        <v>884.4</v>
       </c>
       <c r="I53" t="n">
         <v>875.7963985094499</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.19</v>
       </c>
       <c r="L53" t="n">
-        <v>1.71</v>
+        <v>5.1</v>
       </c>
       <c r="M53" t="n">
         <v>1.84</v>
       </c>
       <c r="N53" t="n">
-        <v>1.72</v>
+        <v>2.26</v>
       </c>
       <c r="O53" t="n">
         <v>-0.9</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.2</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>862.5</v>
+        <v>847</v>
       </c>
       <c r="I54" t="n">
         <v>857.3544448704291</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.48</v>
+        <v>-4.23</v>
       </c>
       <c r="L54" t="n">
-        <v>2.59</v>
+        <v>4.44</v>
       </c>
       <c r="M54" t="n">
         <v>0.05</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>5.15</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>776.1</v>
+        <v>816.05</v>
       </c>
       <c r="I55" t="n">
         <v>814.5927739781366</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>8.369999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="L55" t="n">
         <v>2.48</v>
       </c>
       <c r="M55" t="n">
-        <v>0.72</v>
+        <v>1.4</v>
       </c>
       <c r="N55" t="n">
-        <v>1.26</v>
+        <v>5.47</v>
       </c>
       <c r="O55" t="n">
         <v>-1.66</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.53</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>789.7</v>
+        <v>775.7</v>
       </c>
       <c r="I56" t="n">
         <v>787.3376848936501</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.23</v>
+        <v>-4.94</v>
       </c>
       <c r="L56" t="n">
-        <v>4.05</v>
+        <v>5.15</v>
       </c>
       <c r="M56" t="n">
         <v>0.48</v>
       </c>
       <c r="N56" t="n">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="O56" t="n">
         <v>5.47</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>5.57</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45909.38541666666</v>
+        <v>45909.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>784.05</v>
+        <v>795</v>
       </c>
       <c r="I57" t="n">
         <v>784.8430494258836</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.08</v>
+        <v>-2.49</v>
       </c>
       <c r="L57" t="n">
-        <v>2.23</v>
+        <v>2.59</v>
       </c>
       <c r="M57" t="n">
         <v>0.97</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.97</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45929.38541666666</v>
+        <v>45929.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>879.6</v>
+        <v>872.5</v>
       </c>
       <c r="I58" t="n">
         <v>877.1141595716543</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>10.64</v>
+        <v>9.75</v>
       </c>
       <c r="L58" t="n">
         <v>1.38</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.17</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>921.45</v>
+        <v>927.75</v>
       </c>
       <c r="I59" t="n">
         <v>924.6286619006098</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.61</v>
+        <v>-6.33</v>
       </c>
       <c r="L59" t="n">
-        <v>6.32</v>
+        <v>6.44</v>
       </c>
       <c r="M59" t="n">
         <v>0.27</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.88</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>977</v>
+        <v>968</v>
       </c>
       <c r="I60" t="n">
         <v>972.285369859359</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>48.83333333333334</v>
+        <v>49</v>
       </c>
       <c r="K60" t="n">
-        <v>5.31</v>
+        <v>4.34</v>
       </c>
       <c r="L60" t="n">
         <v>2.11</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.05</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46002.55208333334</v>
+        <v>46003.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>997.6</v>
+        <v>1013.3</v>
       </c>
       <c r="I61" t="n">
         <v>1000.504469164738</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.06</v>
+        <v>-4.68</v>
       </c>
       <c r="L61" t="n">
-        <v>4.12</v>
+        <v>4.8</v>
       </c>
       <c r="M61" t="n">
         <v>0.66</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.58</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1032</v>
+        <v>1004.3</v>
       </c>
       <c r="I62" t="n">
         <v>1011.452703117081</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K62" t="n">
-        <v>1.85</v>
+        <v>-0.89</v>
       </c>
       <c r="L62" t="n">
         <v>4.37</v>
@@ -3975,7 +4718,7 @@
         <v>0.55</v>
       </c>
       <c r="N62" t="n">
-        <v>2.19</v>
+        <v>3.85</v>
       </c>
       <c r="O62" t="n">
         <v>1.06</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.17</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>882.9</v>
+        <v>977.5</v>
       </c>
       <c r="I63" t="n">
         <v>917.2678029019725</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K63" t="n">
-        <v>12.09</v>
+        <v>2.67</v>
       </c>
       <c r="L63" t="n">
         <v>2.76</v>
       </c>
       <c r="M63" t="n">
-        <v>0.85</v>
+        <v>7.71</v>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>10.18</v>
       </c>
       <c r="O63" t="n">
         <v>-3.85</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>13.04</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1009.05</v>
+        <v>958.7</v>
       </c>
       <c r="I64" t="n">
         <v>969.0641969526254</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>3.23</v>
+        <v>-1.92</v>
       </c>
       <c r="L64" t="n">
         <v>4.12</v>
       </c>
       <c r="M64" t="n">
-        <v>1.15</v>
+        <v>4.76</v>
       </c>
       <c r="N64" t="n">
         <v>3.8</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>9.31</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46099.38541666666</v>
+        <v>46099.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>1027.8</v>
+        <v>1034</v>
       </c>
       <c r="I65" t="n">
         <v>1032.348819290155</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.21</v>
+        <v>-7.85</v>
       </c>
       <c r="L65" t="n">
-        <v>7.6</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M65" t="n">
         <v>1.76</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>7.94</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1008.6</v>
+        <v>939.3</v>
       </c>
       <c r="I66" t="n">
         <v>951.8591421111489</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.46</v>
+        <v>-9.16</v>
       </c>
       <c r="L66" t="n">
-        <v>3.38</v>
+        <v>9.51</v>
       </c>
       <c r="M66" t="n">
         <v>1.89</v>
       </c>
       <c r="N66" t="n">
-        <v>2.23</v>
+        <v>6.35</v>
       </c>
       <c r="O66" t="n">
         <v>3.4</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>12.95</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>986.35</v>
+        <v>1060.35</v>
       </c>
       <c r="I67" t="n">
         <v>1013.258328738622</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.01</v>
+        <v>-12.89</v>
       </c>
       <c r="L67" t="n">
-        <v>6.56</v>
+        <v>15.5</v>
       </c>
       <c r="M67" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="O67" t="n">
         <v>-6.35</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>10.95</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1344.8</v>
+        <v>1262.7</v>
       </c>
       <c r="I68" t="n">
         <v>1304.388638662899</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K68" t="n">
-        <v>26.83</v>
+        <v>19.08</v>
       </c>
       <c r="L68" t="n">
         <v>4.37</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>14.54</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46168.38541666666</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>1403.9</v>
+        <v>1488.7</v>
       </c>
       <c r="I69" t="n">
         <v>1411.544674087546</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>-11.18</v>
+        <v>-17.9</v>
       </c>
       <c r="L69" t="n">
-        <v>12.77</v>
+        <v>17.92</v>
       </c>
       <c r="M69" t="n">
         <v>3.41</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.33</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46239.55208333334</v>
+        <v>46240.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1633</v>
+        <v>1625.7</v>
       </c>
       <c r="I70" t="n">
         <v>1632.012218690735</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>71</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>9.69</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L70" t="n">
         <v>5.86</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>5.7</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1374.1</v>
+        <v>1431.2</v>
       </c>
       <c r="I71" t="n">
         <v>1428.490335896756</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K71" t="n">
-        <v>15.48</v>
+        <v>11.96</v>
       </c>
       <c r="L71" t="n">
         <v>2.85</v>
@@ -4488,7 +5339,7 @@
         <v>2.34</v>
       </c>
       <c r="N71" t="n">
-        <v>2.05</v>
+        <v>4.18</v>
       </c>
       <c r="O71" t="n">
         <v>-1.56</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>7.92</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46289.38541666666</v>
+        <v>46289.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>1353</v>
+        <v>1340</v>
       </c>
       <c r="I72" t="n">
         <v>1346.882045131265</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.46</v>
+        <v>-6.37</v>
       </c>
       <c r="L72" t="n">
-        <v>6.15</v>
+        <v>6.71</v>
       </c>
       <c r="M72" t="n">
         <v>0.83</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>5.65</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46309.38541666666</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="H73" t="n">
-        <v>1347.4</v>
+        <v>1361</v>
       </c>
       <c r="I73" t="n">
         <v>1357.663584833879</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.55</v>
+        <v>-1.57</v>
       </c>
       <c r="L73" t="n">
         <v>3.7</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>7.75</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1292.1</v>
+        <v>1201.8</v>
       </c>
       <c r="I74" t="n">
         <v>1286.803657419443</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.06</v>
+        <v>-11.7</v>
       </c>
       <c r="L74" t="n">
-        <v>5.44</v>
+        <v>11.72</v>
       </c>
       <c r="M74" t="n">
         <v>0.8</v>
       </c>
       <c r="N74" t="n">
-        <v>3.18</v>
+        <v>5.58</v>
       </c>
       <c r="O74" t="n">
         <v>5.02</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,12 @@
       <c r="Q75" t="n">
         <v>6</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6821,7 +7726,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="6">
@@ -6831,7 +7736,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6841,7 +7746,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="8">
@@ -6851,7 +7756,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6861,7 +7766,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -6871,7 +7776,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="11">
@@ -6881,7 +7786,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -6891,7 +7796,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6901,7 +7806,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72.59999999999999</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="14">
@@ -6911,7 +7816,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.18</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="15">
@@ -6921,7 +7826,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.78</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="16">
@@ -6931,7 +7836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.55</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="17">
@@ -6941,7 +7846,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73.88</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="18">
@@ -6951,7 +7856,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="19">
@@ -6961,7 +7866,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.4</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="20">
@@ -6971,7 +7876,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.38</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="21">
@@ -6981,7 +7886,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.11</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="22">
@@ -6991,7 +7896,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -7001,7 +7906,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -7011,7 +7916,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="25">
@@ -7021,7 +7926,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.4</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -7031,7 +7936,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.55</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="27">
@@ -7041,7 +7946,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.49</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="28">
@@ -7051,7 +7956,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
